--- a/validation/expert_reviews/E4_extraction_review.xlsx
+++ b/validation/expert_reviews/E4_extraction_review.xlsx
@@ -580,7 +580,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Review workbook — Haoran</t>
+          <t>Review workbook — E4</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Haoran    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E4    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Haoran</t>
+          <t>Rating — E4</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Haoran    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E4    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Haoran</t>
+          <t>Rating — E4</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Haoran    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E4    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Haoran</t>
+          <t>Rating — E4</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Haoran    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E4    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Haoran</t>
+          <t>Rating — E4</t>
         </is>
       </c>
     </row>
@@ -3487,7 +3487,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Haoran    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E4    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Haoran</t>
+          <t>Rating — E4</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Haoran    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E4    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -3942,7 +3942,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Haoran</t>
+          <t>Rating — E4</t>
         </is>
       </c>
     </row>
@@ -4238,7 +4238,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Haoran    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E4    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -4298,6 +4298,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -4413,6 +4414,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -4755,7 +4757,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Haoran    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E4    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -4815,6 +4817,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -4930,6 +4933,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -5272,7 +5276,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Haoran    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E4    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -5332,6 +5336,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -5447,6 +5452,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -5789,7 +5795,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Haoran    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E4    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -5849,6 +5855,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -5964,6 +5971,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -6306,7 +6314,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Haoran    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E4    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -6366,6 +6374,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -6481,6 +6490,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -6823,7 +6833,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Haoran    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E4    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -6883,6 +6893,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -6998,6 +7009,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -7340,7 +7352,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Haoran    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E4    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -7400,6 +7412,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -7515,6 +7528,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -7862,7 +7876,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Haoran    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E4    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -7881,7 +7895,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Haoran</t>
+          <t>Rating — E4</t>
         </is>
       </c>
     </row>
